--- a/output/OFAPDFDATAUpload (1).xlsx
+++ b/output/OFAPDFDATAUpload (1).xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DZ24"/>
+  <dimension ref="A1:DZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6636,138 +6636,6 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="inlineStr"/>
-      <c r="AO24" t="inlineStr"/>
-      <c r="AP24" t="inlineStr"/>
-      <c r="AQ24" t="inlineStr"/>
-      <c r="AR24" t="inlineStr"/>
-      <c r="AS24" t="inlineStr"/>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AU24" t="inlineStr"/>
-      <c r="AV24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr"/>
-      <c r="AX24" t="inlineStr"/>
-      <c r="AY24" t="inlineStr"/>
-      <c r="AZ24" t="inlineStr"/>
-      <c r="BA24" t="inlineStr"/>
-      <c r="BB24" t="inlineStr"/>
-      <c r="BC24" t="inlineStr"/>
-      <c r="BD24" t="inlineStr"/>
-      <c r="BE24" t="inlineStr"/>
-      <c r="BF24" t="inlineStr"/>
-      <c r="BG24" t="inlineStr"/>
-      <c r="BH24" t="inlineStr"/>
-      <c r="BI24" t="inlineStr"/>
-      <c r="BJ24" t="inlineStr"/>
-      <c r="BK24" t="inlineStr"/>
-      <c r="BL24" t="inlineStr"/>
-      <c r="BM24" t="inlineStr"/>
-      <c r="BN24" t="inlineStr"/>
-      <c r="BO24" t="inlineStr"/>
-      <c r="BP24" t="inlineStr"/>
-      <c r="BQ24" t="inlineStr"/>
-      <c r="BR24" t="inlineStr"/>
-      <c r="BS24" t="inlineStr"/>
-      <c r="BT24" t="inlineStr"/>
-      <c r="BU24" t="inlineStr"/>
-      <c r="BV24" t="inlineStr"/>
-      <c r="BW24" t="inlineStr"/>
-      <c r="BX24" t="inlineStr"/>
-      <c r="BY24" t="inlineStr"/>
-      <c r="BZ24" t="inlineStr"/>
-      <c r="CA24" t="inlineStr"/>
-      <c r="CB24" t="inlineStr"/>
-      <c r="CC24" t="inlineStr"/>
-      <c r="CD24" t="inlineStr"/>
-      <c r="CE24" t="inlineStr"/>
-      <c r="CF24" t="inlineStr"/>
-      <c r="CG24" t="inlineStr"/>
-      <c r="CH24" t="inlineStr"/>
-      <c r="CI24" t="inlineStr"/>
-      <c r="CJ24" t="inlineStr"/>
-      <c r="CK24" t="inlineStr"/>
-      <c r="CL24" t="inlineStr"/>
-      <c r="CM24" t="inlineStr"/>
-      <c r="CN24" t="inlineStr"/>
-      <c r="CO24" t="inlineStr"/>
-      <c r="CP24" t="inlineStr"/>
-      <c r="CQ24" t="inlineStr"/>
-      <c r="CR24" t="inlineStr"/>
-      <c r="CS24" t="inlineStr"/>
-      <c r="CT24" t="inlineStr"/>
-      <c r="CU24" t="inlineStr"/>
-      <c r="CV24" t="inlineStr"/>
-      <c r="CW24" t="inlineStr"/>
-      <c r="CX24" t="inlineStr"/>
-      <c r="CY24" t="inlineStr"/>
-      <c r="CZ24" t="inlineStr"/>
-      <c r="DA24" t="inlineStr"/>
-      <c r="DB24" t="inlineStr"/>
-      <c r="DC24" t="inlineStr"/>
-      <c r="DD24" t="inlineStr"/>
-      <c r="DE24" t="inlineStr"/>
-      <c r="DF24" t="inlineStr"/>
-      <c r="DG24" t="inlineStr"/>
-      <c r="DH24" t="inlineStr"/>
-      <c r="DI24" t="inlineStr"/>
-      <c r="DJ24" t="inlineStr"/>
-      <c r="DK24" t="inlineStr"/>
-      <c r="DL24" t="inlineStr"/>
-      <c r="DM24" t="inlineStr"/>
-      <c r="DN24" t="inlineStr"/>
-      <c r="DO24" t="inlineStr"/>
-      <c r="DP24" t="inlineStr"/>
-      <c r="DQ24" t="inlineStr"/>
-      <c r="DR24" t="inlineStr"/>
-      <c r="DS24" t="inlineStr"/>
-      <c r="DT24" t="inlineStr"/>
-      <c r="DU24" t="inlineStr"/>
-      <c r="DV24" t="inlineStr"/>
-      <c r="DW24" t="inlineStr"/>
-      <c r="DX24" t="inlineStr"/>
-      <c r="DY24" t="inlineStr"/>
-      <c r="DZ24" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
